--- a/JsonConverter/ExcelFiles/StatusEffectData.xlsx
+++ b/JsonConverter/ExcelFiles/StatusEffectData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
   <si>
     <t>아이디</t>
   </si>
@@ -136,6 +136,9 @@
     <t>소울 공명</t>
   </si>
   <si>
+    <t>StatModifier</t>
+  </si>
+  <si>
     <t>RefreshDuration</t>
   </si>
   <si>
@@ -161,9 +164,6 @@
   </si>
   <si>
     <t>플레이어의 체력이 최대일 때 일반 공격 쿨다운을 15% 감소시킵니다.</t>
-  </si>
-  <si>
-    <t>StatModifier</t>
   </si>
   <si>
     <t>buff_taunt</t>
@@ -311,15 +311,15 @@
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -842,9 +842,11 @@
         <v>40</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="D8" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="E8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6">
         <v>7.0</v>
@@ -855,10 +857,10 @@
         <v>0.1</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="6"/>
@@ -868,15 +870,17 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="D9" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="E9" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="6">
         <v>7.0</v>
@@ -887,28 +891,30 @@
         <v>10.0</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L9" s="8"/>
-      <c r="M9" s="11"/>
+      <c r="M9" s="12"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="D10" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="E10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" s="6">
         <v>7.0</v>
@@ -922,7 +928,7 @@
         <v>35</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="6"/>
@@ -932,19 +938,19 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="12" t="s">
         <v>49</v>
       </c>
+      <c r="C11" s="13" t="s">
+        <v>50</v>
+      </c>
       <c r="D11" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" s="6">
         <v>5.0</v>
@@ -955,10 +961,10 @@
         <v>0.15</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="6"/>
@@ -976,9 +982,11 @@
       <c r="C12" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="E12" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" s="6">
         <v>4.0</v>
@@ -1001,16 +1009,16 @@
       <c r="P12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="11"/>
       <c r="F13" s="6"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
@@ -1033,24 +1041,24 @@
       <c r="A14" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D14" s="6"/>
-      <c r="E14" s="14"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="6"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="16">
         <v>10.0</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="11" t="s">
         <v>30</v>
       </c>
       <c r="L14" s="8"/>
@@ -4732,17 +4740,17 @@
       <c r="P218" s="9"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="12"/>
-      <c r="B219" s="12"/>
-      <c r="C219" s="12"/>
-      <c r="D219" s="12"/>
-      <c r="E219" s="12"/>
-      <c r="F219" s="12"/>
+      <c r="A219" s="13"/>
+      <c r="B219" s="13"/>
+      <c r="C219" s="13"/>
+      <c r="D219" s="13"/>
+      <c r="E219" s="13"/>
+      <c r="F219" s="13"/>
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="7"/>
-      <c r="J219" s="12"/>
-      <c r="K219" s="12"/>
+      <c r="J219" s="13"/>
+      <c r="K219" s="13"/>
       <c r="L219" s="17"/>
       <c r="M219" s="18"/>
       <c r="N219" s="19"/>
@@ -4750,17 +4758,17 @@
       <c r="P219" s="19"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="12"/>
-      <c r="B220" s="12"/>
-      <c r="C220" s="12"/>
-      <c r="D220" s="12"/>
-      <c r="E220" s="12"/>
-      <c r="F220" s="12"/>
+      <c r="A220" s="13"/>
+      <c r="B220" s="13"/>
+      <c r="C220" s="13"/>
+      <c r="D220" s="13"/>
+      <c r="E220" s="13"/>
+      <c r="F220" s="13"/>
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="7"/>
-      <c r="J220" s="12"/>
-      <c r="K220" s="12"/>
+      <c r="J220" s="13"/>
+      <c r="K220" s="13"/>
       <c r="L220" s="17"/>
       <c r="M220" s="18"/>
       <c r="N220" s="19"/>
